--- a/DesignTable/Data/Table/Tables/skill_effect.xlsx
+++ b/DesignTable/Data/Table/Tables/skill_effect.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oh\Desktop\DesignGenerator\Data\Data_Export\Table\Tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4939E64C-7B69-4F7B-9982-67CD3836B15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{24C10ED1-87A3-4556-A187-05572B708FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{793C827D-AC6E-4BA0-9FF8-084CEF82D22E}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{793C827D-AC6E-4BA0-9FF8-084CEF82D22E}"/>
   </bookViews>
   <sheets>
     <sheet name="record" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>ColumnName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TableID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>effect_Id</t>
   </si>
   <si>
@@ -107,6 +103,14 @@
   </si>
   <si>
     <t>Assets/Res/Effect/Hits/HitFolder/Prefabs/vfxStretch1.prefab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FieldNo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TableId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +171,10 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -186,7 +193,7 @@
 
 <file path=xl/xmlMaps.xml><?xml version="1.0" encoding="utf-8"?>
 <MapInfo xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" SelectionNamespaces="">
-  <Schema ID="Schema1">
+  <Schema ID="Schema2">
     <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="">
       <xsd:element nillable="true" name="skill_effect">
         <xsd:complexType>
@@ -201,6 +208,7 @@
                 <xsd:attribute name="EnumID" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="IDRule" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="StringHashIds" form="unqualified" type="xsd:string"/>
+                <xsd:attribute name="FieldNo" form="unqualified" type="xsd:string"/>
                 <xsd:attribute name="TableId" form="unqualified" type="xsd:string"/>
               </xsd:complexType>
             </xsd:element>
@@ -217,7 +225,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="1" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema1" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="4" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -226,10 +234,10 @@
   <autoFilter ref="A1:B4" xr:uid="{70A41559-E888-494F-A26B-AD59FC5798F5}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5783BD51-DC0F-4356-8A76-CEFE8C90D864}" uniqueName="effect_Id" name="effect_Id">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{2830F923-D3E9-4744-BD7C-FB25EB826204}" uniqueName="effect_path" name="effect_path" dataDxfId="0">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{2830F923-D3E9-4744-BD7C-FB25EB826204}" uniqueName="effect_path" name="effect_path" dataDxfId="1">
+      <xmlColumnPr mapId="4" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -237,35 +245,38 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{36022407-68B3-40F7-B651-C32964453326}" name="표1" displayName="표1" ref="A1:I3" tableType="xml" totalsRowShown="0">
-  <autoFilter ref="A1:I3" xr:uid="{36022407-68B3-40F7-B651-C32964453326}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{36022407-68B3-40F7-B651-C32964453326}" name="표1" displayName="표1" ref="A1:J3" tableType="xml" totalsRowShown="0">
+  <autoFilter ref="A1:J3" xr:uid="{36022407-68B3-40F7-B651-C32964453326}"/>
+  <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05EF01BD-F146-4E19-A0A0-20A473C06AA8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CC450716-F59F-46DA-819F-7026FA08BD01}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{628DB6D9-5545-43B3-893B-91A16CA46186}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9F2F9594-7FF2-467A-BE1F-BE756BA21361}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D3D2748-DC14-40BD-8393-46A3D7D44F91}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB494AD4-624C-4027-A7C7-D6189F5708A7}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BE9F8CC6-66AB-45F6-95C6-9D9340943A84}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{6DD89B65-AAD8-4A8C-8F7E-D75D95152F75}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{E6FC3AFF-15DE-4B36-B8A4-B1D3E3559212}" uniqueName="TableId" name="TableID">
-      <xmlColumnPr mapId="1" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{E6FC3AFF-15DE-4B36-B8A4-B1D3E3559212}" uniqueName="FieldNo" name="FieldNo">
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{94CD4585-A84D-4338-9EB9-6BB15F5819C8}" uniqueName="TableId" name="TableId" dataDxfId="0">
+      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -577,18 +588,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -596,7 +607,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -604,7 +615,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -618,10 +629,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F90862E-140D-44A7-A78A-2F31983E25C1}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -647,64 +658,73 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1015</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>1015</v>
       </c>
     </row>

--- a/DesignTable/Data/Table/Tables/skill_effect.xlsx
+++ b/DesignTable/Data/Table/Tables/skill_effect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{24C10ED1-87A3-4556-A187-05572B708FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB388803-380F-48DA-BF89-4061FB4D211B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{793C827D-AC6E-4BA0-9FF8-084CEF82D22E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="4" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="6" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -234,10 +234,10 @@
   <autoFilter ref="A1:B4" xr:uid="{70A41559-E888-494F-A26B-AD59FC5798F5}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5783BD51-DC0F-4356-8A76-CEFE8C90D864}" uniqueName="effect_Id" name="effect_Id">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2830F923-D3E9-4744-BD7C-FB25EB826204}" uniqueName="effect_path" name="effect_path" dataDxfId="1">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -249,34 +249,34 @@
   <autoFilter ref="A1:J3" xr:uid="{36022407-68B3-40F7-B651-C32964453326}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05EF01BD-F146-4E19-A0A0-20A473C06AA8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CC450716-F59F-46DA-819F-7026FA08BD01}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{628DB6D9-5545-43B3-893B-91A16CA46186}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9F2F9594-7FF2-467A-BE1F-BE756BA21361}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D3D2748-DC14-40BD-8393-46A3D7D44F91}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB494AD4-624C-4027-A7C7-D6189F5708A7}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BE9F8CC6-66AB-45F6-95C6-9D9340943A84}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{6DD89B65-AAD8-4A8C-8F7E-D75D95152F75}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E6FC3AFF-15DE-4B36-B8A4-B1D3E3559212}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{94CD4585-A84D-4338-9EB9-6BB15F5819C8}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="4" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/skill_effect.xlsx
+++ b/DesignTable/Data/Table/Tables/skill_effect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB388803-380F-48DA-BF89-4061FB4D211B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3017B490-8DBE-4760-874E-843B4747E359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{793C827D-AC6E-4BA0-9FF8-084CEF82D22E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="6" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="8" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -234,10 +234,10 @@
   <autoFilter ref="A1:B4" xr:uid="{70A41559-E888-494F-A26B-AD59FC5798F5}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5783BD51-DC0F-4356-8A76-CEFE8C90D864}" uniqueName="effect_Id" name="effect_Id">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2830F923-D3E9-4744-BD7C-FB25EB826204}" uniqueName="effect_path" name="effect_path" dataDxfId="1">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -249,34 +249,34 @@
   <autoFilter ref="A1:J3" xr:uid="{36022407-68B3-40F7-B651-C32964453326}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05EF01BD-F146-4E19-A0A0-20A473C06AA8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CC450716-F59F-46DA-819F-7026FA08BD01}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{628DB6D9-5545-43B3-893B-91A16CA46186}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9F2F9594-7FF2-467A-BE1F-BE756BA21361}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D3D2748-DC14-40BD-8393-46A3D7D44F91}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB494AD4-624C-4027-A7C7-D6189F5708A7}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BE9F8CC6-66AB-45F6-95C6-9D9340943A84}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{6DD89B65-AAD8-4A8C-8F7E-D75D95152F75}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E6FC3AFF-15DE-4B36-B8A4-B1D3E3559212}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{94CD4585-A84D-4338-9EB9-6BB15F5819C8}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="6" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>

--- a/DesignTable/Data/Table/Tables/skill_effect.xlsx
+++ b/DesignTable/Data/Table/Tables/skill_effect.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ProjectT\DesignTable\Data\Table\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3017B490-8DBE-4760-874E-843B4747E359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95F13A83-EA0F-4C5E-8E01-AA587AD2D868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{793C827D-AC6E-4BA0-9FF8-084CEF82D22E}"/>
   </bookViews>
@@ -225,7 +225,7 @@
       </xsd:element>
     </xsd:schema>
   </Schema>
-  <Map ID="8" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
+  <Map ID="9" Name="skill_effect_맵" RootElement="skill_effect" SchemaID="Schema2" ShowImportExportValidationErrors="false" AutoFit="true" Append="false" PreserveSortAFLayout="true" PreserveFormat="true"/>
 </MapInfo>
 </file>
 
@@ -234,10 +234,10 @@
   <autoFilter ref="A1:B4" xr:uid="{70A41559-E888-494F-A26B-AD59FC5798F5}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{5783BD51-DC0F-4356-8A76-CEFE8C90D864}" uniqueName="effect_Id" name="effect_Id">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/record/effect_Id" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2830F923-D3E9-4744-BD7C-FB25EB826204}" uniqueName="effect_path" name="effect_path" dataDxfId="1">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/record/effect_path" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -249,34 +249,34 @@
   <autoFilter ref="A1:J3" xr:uid="{36022407-68B3-40F7-B651-C32964453326}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{05EF01BD-F146-4E19-A0A0-20A473C06AA8}" uniqueName="ColumnName" name="ColumnName">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@ColumnName" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{CC450716-F59F-46DA-819F-7026FA08BD01}" uniqueName="Type" name="Type">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@Type" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{628DB6D9-5545-43B3-893B-91A16CA46186}" uniqueName="IsClient" name="IsClient">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@IsClient" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{9F2F9594-7FF2-467A-BE1F-BE756BA21361}" uniqueName="IsServer" name="IsServer">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@IsServer" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{0D3D2748-DC14-40BD-8393-46A3D7D44F91}" uniqueName="PK" name="PK">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@PK" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BB494AD4-624C-4027-A7C7-D6189F5708A7}" uniqueName="EnumID" name="EnumID">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@EnumID" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{BE9F8CC6-66AB-45F6-95C6-9D9340943A84}" uniqueName="IDRule" name="IDRule">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@IDRule" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{6DD89B65-AAD8-4A8C-8F7E-D75D95152F75}" uniqueName="StringHashIds" name="StringHashIds">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@StringHashIds" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{E6FC3AFF-15DE-4B36-B8A4-B1D3E3559212}" uniqueName="FieldNo" name="FieldNo">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@FieldNo" xmlDataType="string"/>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{94CD4585-A84D-4338-9EB9-6BB15F5819C8}" uniqueName="TableId" name="TableId" dataDxfId="0">
-      <xmlColumnPr mapId="8" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
+      <xmlColumnPr mapId="9" xpath="/skill_effect/verify/@TableId" xmlDataType="string"/>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
